--- a/artfynd/A 31435-2024 artfynd.xlsx
+++ b/artfynd/A 31435-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>119747840</v>
       </c>
       <c r="B3" t="n">
-        <v>89441</v>
+        <v>89458</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
